--- a/data/QuestionBank_AirLaw_RPL_v3.xlsx
+++ b/data/QuestionBank_AirLaw_RPL_v3.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CASR 91.330 item 6 requires the aircraft that has the other aircraft on its right to give way; therefore the aircraft with the other on its left has right of way.</t>
+          <t>CASR 91.330 requires the aircraft that has another aircraft on its right to give way; the aircraft with the other on its left therefore has right of way.</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CASR 91.330 item 4 requires the overtaking aircraft to give way; the aircraft being overtaken has right of way.</t>
+          <t>CASR 91.330 requires an overtaking aircraft to give way; the aircraft being overtaken has right of way.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CASR 91.330 item 5 requires a power-driven aircraft to give way to an unpowered glider.</t>
+          <t>CASR 91.330 requires a power-driven aircraft to give way to an unpowered glider where their flight paths converge.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>CASR 91.330 item 3 requires the higher aircraft to give way to the lower aircraft on approach.</t>
+          <t>CASR 91.330 requires the higher of two heavier-than-air aircraft on approach to land to give way to the lower aircraft.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>CASR 91.330 item 1 requires all other aircraft to give way to an aircraft compelled to land.</t>
+          <t>CASR 91.330 requires every other aircraft to give way to an aircraft that is in an emergency and compelled to land.</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>AIP ENR 1.1 section 9.4 — Circuit Height</t>
+          <t>AIP ENR 1.1 section 9.2 — Circuit Information</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4281,37 +4281,37 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>The pilot discovers a defect during flight that affects the safe operation of the aircraft. The PIC must:</t>
+          <t>A defect that may affect the safe operation of the aircraft is found in flight. The pilot in command must:</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>land at the nearest suitable aerodrome</t>
+          <t>log it after landing only</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>continue to destination and report at landing</t>
+          <t>continue if within MEL limits</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>write up the defect on the MR after landing only</t>
+          <t>divert immediately to the nearest aerodrome</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>ignore the defect if within MEL limits</t>
+          <t>assess and not continue if safety affected</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>CASR 91.215 requires the PIC to ensure safe operation of the aircraft. A defect affecting safe operation means the PIC must land at the nearest suitable aerodrome (CASR 91.680 for emergencies) and the defect must be recorded.</t>
+          <t>CASR 91.215 places responsibility for the safe operation of the aircraft with the pilot in command. The PIC must assess any in-flight defect and stop the flight (or take other safe action) if it affects safe operation. Immediate diversion to the nearest suitable aerodrome is mandated only when the situation amounts to an emergency under CASR 91.680.</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAYDAY MAYDAY MAYDAY FUEL</t>
+          <t>MAYDAY, MAYDAY, MAYDAY FUEL</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Part 91 MOS 19.06(4) requires the PIC to declare emergency fuel by broadcasting "MAYDAY, MAYDAY, MAYDAY FUEL" when landing with less than final reserve fuel.</t>
+          <t>Part 91 MOS 19.06(4) requires the pilot in command to declare a situation of "emergency fuel" by broadcasting "MAYDAY, MAYDAY, MAYDAY FUEL" when, at any time during a flight, the aircraft will land at the nearest aerodrome where a safe landing can be made with less than final reserve fuel remaining.</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>not at TO/LDG, and when PIC directs</t>
+          <t>not during take-off or landing or when PIC directs</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>morning civil twilight to evening civil twilight</t>
+          <t>beginning of morning civil twilight to end of evening civil twilight</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
